--- a/output/graficos_dimensiones/comunal_e_mat_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2023_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:42</t>
+    <t xml:space="preserve">2026-09-10 00:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2023_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:51</t>
+    <t xml:space="preserve">2026-09-18 11:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2023_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:00</t>
+    <t xml:space="preserve">2026-09-23 14:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -863,7 +863,9 @@
       <c r="C21" s="2" t="n">
         <v>16206</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" s="2" t="n">
+        <v>2023</v>
+      </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
@@ -876,7 +878,9 @@
       <c r="C22" s="2" t="n">
         <v>16303</v>
       </c>
-      <c r="D22" s="2"/>
+      <c r="D22" s="2" t="n">
+        <v>2023</v>
+      </c>
       <c r="E22" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2023_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:20</t>
+    <t xml:space="preserve">2026-10-02 15:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2023_nuble.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">San Fabián</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Ñiquén</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:32</t>
+    <t xml:space="preserve">2026-10-04 10:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2023_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:04</t>
+    <t xml:space="preserve">2026-10-05 14:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
